--- a/plans.xlsx
+++ b/plans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\MyAllProjects\Wedding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0010D5-9892-42BF-8131-7DBE52371735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3E1AFF-DBEF-4FCA-A603-5E0423019839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{233B6720-A9C3-4500-81FF-29BB74E25307}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">PlanS </t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>add songs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix instagram Screen size </t>
+  </si>
+  <si>
+    <t>Fix audio for mobiles</t>
   </si>
 </sst>
 </file>
@@ -434,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{215D8201-1499-4823-BA1F-BBC86E98A799}">
-  <dimension ref="I5:N11"/>
+  <dimension ref="I5:N16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="51.85546875" customWidth="1"/>
@@ -458,6 +464,9 @@
       </c>
     </row>
     <row r="8" spans="9:14" x14ac:dyDescent="0.25">
+      <c r="I8" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="N8" t="s">
         <v>5</v>
       </c>
@@ -467,14 +476,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="9:14" x14ac:dyDescent="0.25">
-      <c r="I10" t="s">
+    <row r="14" spans="9:14" x14ac:dyDescent="0.25">
+      <c r="I14" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="9:14" x14ac:dyDescent="0.25">
-      <c r="I11" s="2" t="s">
-        <v>7</v>
+    <row r="15" spans="9:14" x14ac:dyDescent="0.25">
+      <c r="I15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="9:14" x14ac:dyDescent="0.25">
+      <c r="I16" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
